--- a/batch_mobile.xlsx
+++ b/batch_mobile.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ2"/>
+  <dimension ref="A1:AR2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -463,6 +463,7 @@
     <col width="10" customWidth="1" min="41" max="41"/>
     <col width="10" customWidth="1" min="42" max="42"/>
     <col width="10" customWidth="1" min="43" max="43"/>
+    <col width="10" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -678,7 +679,12 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>Flagged (low confidence)</t>
+          <t>Flagged Questions</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Confidence</t>
         </is>
       </c>
     </row>
@@ -687,47 +693,214 @@
         <v>1</v>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>Too few circles remain (2) after outlier removal.</t>
+        </is>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
